--- a/Data/dtContent.xlsx
+++ b/Data/dtContent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupecgi-my.sharepoint.com/personal/ali_mahjoub_cgi_com/Documents/Documents/UiPath/AI Social Media Manager/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="11_566DDBBDCB27296BF063027BA00025B0F08500BA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38B47333-0FEE-46A9-AED4-A18D374A90E1}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="11_566DDBBDCB27296BF063027BA00025B0F08500BA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85F9E2E6-A260-4F8B-9CE5-A0C363C1E81C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,317 +85,303 @@
     <t>Ask HN: What are some good technology blogs to follow?</t>
   </si>
   <si>
-    <t>Solo founders succeed by choosing boring, stable tech stacks over flashy new tools. 🛠️ The key is stability, proven performance, and focusing on customers—not reinventing the stack. [1][2]</t>
-  </si>
-  <si>
-    <t>Why do one-person internet companies thrive with boring technology? Because boring = stable, supported, and time-tested. Solo founders who skip the hype build faster and scale smarter. [1][2]</t>
-  </si>
-  <si>
-    <t>Strategic Advantage of Boring Tech for Solo Founders: They prioritize stability, broad support, and alignment with existing skills. This approach reduces risk and accelerates product delivery. [1][2]</t>
-  </si>
-  <si>
-    <t>One-person Internet companies don’t need React drama. They need boring, stable tech that works. 🚫 Flashy ✅ Proven [1][2]</t>
-  </si>
-  <si>
-    <t>POV: You’re a solo dev building a profitable startup. Skip the hype. Use boring tech. It’s stable, supported, and gets you to customers faster. 💻 [1][2]</t>
-  </si>
-  <si>
-    <t>The secret to a one-person Internet company isn’t cutting-edge tech—it’s boring, stable technology that has stood the test of time.</t>
-  </si>
-  <si>
-    <t>Stop chasing new frameworks. Start building with boring, proven tools. Tag a solo founder who needs to hear this.</t>
-  </si>
-  <si>
-    <t>#SoloFounder #BoringTech #StartupTips #TechStack #WebDevelopment #IndieHacker #SoftwareEngineering #BuildInPublic</t>
-  </si>
-  <si>
-    <t>🚨 Your brain isn’t weak—tech is hijacking it. Former Google design ethicist Tristan Harris reveals how apps like Instagram use variable rewards (likes, messages) on unpredictable schedules to trigger dopamine loops and compulsive checking. It’s not your fault; it’s engineered. [1][4]</t>
-  </si>
-  <si>
-    <t>Technology isn’t just distracting us—it’s hijacking our minds. From fake ‘free choices’ to bottomless content flows, platforms like Facebook exploit psychological vulnerabilities (like variable rewards) to keep us scrolling even when we’re not engaged. Awareness is the first step to reclaiming control. [2][3]</t>
-  </si>
-  <si>
-    <t>The tech industry is manipulating human cognition at scale. Tristan Harris, former Google product manager, argues that social media platforms systematically hijack attention through variable rewards, illusion of choice, and infinite content flows. This isn’t personal failure—it’s a design crisis requiring ethical redesign and business accountability. [3][4]</t>
-  </si>
-  <si>
-    <t>🧠 Your mind is being hijacked. Not by aliens, but by apps. Former Google ethicist Tristan Harris says Instagram, Facebook &amp; Twitter use variable rewards (likes, msgs) on random schedules to trigger dopamine addiction. It’s engineered—not your fault. Awareness = first step to freedom. [1][4]</t>
-  </si>
-  <si>
-    <t>Your brain isn’t broken—tech is hijacking it 😵‍💫 Apps like TikTok &amp; Instagram use variable rewards (likes, comments) on NO schedule to make you CHECK COMPULSIVELY. It’s dopamine engineering. Former Google designer Tristan Harris says: ‘It’s not you—it’s the design.’ [1][4]</t>
-  </si>
-  <si>
-    <t>Your mind isn’t weak—technology is hijacking it.</t>
-  </si>
-  <si>
-    <t>Learn how to spot hijacking techniques and reclaim your attention. Read the full breakdown of Tristan Harris’s findings on tech addiction.</t>
-  </si>
-  <si>
-    <t>#TechHijack #TristanHarris #SocialMediaAddiction #VariableRewards #DigitalWellness #TimeWellSpent #MindHijacked #TechEthics #AttentionEconomy #HumanTech</t>
-  </si>
-  <si>
-    <t>Feeling completely disillusioned with tech? Here’s how to reconnect with what matters beyond screens and algorithms. 💔📵</t>
-  </si>
-  <si>
-    <t>So many people are feeling exhausted by technology right now. Let’s talk about why—and how to find balance again.</t>
-  </si>
-  <si>
-    <t>The growing disillusionment with technology reflects deeper concerns about automation, privacy, and human agency. Leaders must address these sentiment shifts strategically.</t>
-  </si>
-  <si>
-    <t>Tech disillusionment is hitting hard. Over 1,500 Reddit users are saying they’re done with the grind. Are you feeling it too? 🛑📱</t>
-  </si>
-  <si>
-    <t>POV: You’re tired of tech taking over your life. Here’s why so many are quitting the digital hustle—and what to do instead. 🖥️❌</t>
-  </si>
-  <si>
-    <t>Why are millions suddenly ditching tech—and should you follow?</t>
-  </si>
-  <si>
-    <t>Share your story: What’s one tech habit you’re quitting this week? 👇</t>
-  </si>
-  <si>
-    <t>#TechDisillusionment #DigitalBurnout #QuitTech #MentalHealth #TechOverload #RealLife #MindfulTech #SocialMediaTrend</t>
-  </si>
-  <si>
-    <t>🛑 Stop chasing the 'newest' tech stack. The viral Reddit trend 'Choose Boring Technology' is back with 1,357 upvotes. 📉 Why? Because stable, well-understood tools let you focus on what actually matters: solving problems. Use what you know. Ship faster. Boring wins. 🚀
-#TechTrends #BoringTech #SoftwareEngineering #DevLife #StabilityFirst</t>
-  </si>
-  <si>
-    <t>The tech world is buzzing about a simple but powerful idea: 'Choose Boring Technology.' A recent Reddit post in the luu subreddit sparked over 1,300 upvotes and 344 comments, urging developers to stick with tools they already know. 🧠 Why? Well-understood tech has known failure modes, reduces risk, and lets teams focus on solving real problems instead of wrestling with new frameworks. If you're building something mission-critical, boring might just be brilliant. 💡
-What's your go-to 'boring' tech stack?</t>
-  </si>
-  <si>
-    <t>🔥 Trend Alert: 'Choose Boring Technology' is dominating tech conversations on Reddit (luu subreddit, 1,357 upvotes).
-In an era of AI-generated code and constant innovation, the most actionable advice is counterintuitive: use what you already know. 🛠️
-Key takeaways from the trend:
-✅ Prefer well-understood tech with known failure modes.
-✅ Minimize your toolkit to cover your entire problem domain.
-✅ Resist using AI as an excuse to adopt multiple new technologies simultaneously.
-Stability &gt; Novelty when building mission-critical systems. Are you reinventing your stack or refining what works?
-#SoftwareEngineering #TechStrategy #BoringTechnology #AIInDevelopment #EngineeringLeadership</t>
-  </si>
-  <si>
-    <t>🚨 Reddit is roaring: 'Choose Boring Technology' has 1,357 upvotes &amp; 344 comments.
-The rule: Use what you know. Not the newest framework.
-Why? Known failure modes + focus on real problems = less risk. 🛡️
-Boring wins when shipping mission-critical code. 🚀
-#BoringTech #DevTwitter #SoftwareEngineering #AI</t>
-  </si>
-  <si>
-    <t>POV: You're a dev tempted by the latest shiny framework… but then you see this Reddit trend.
-📌 'Choose Boring Technology' = 1,357 upvotes 🔥
-✅ Use what you know
-✅ Known failure modes
-✅ Focus on solving problems, not learning new tools
-Shiny = risky. Boring = reliable. 🛠️
-Tag a dev who needs to hear this! 👇
-#TechTips #SoftwareEngineer #BoringTech #DevLife #CodingTrends</t>
-  </si>
-  <si>
-    <t>The viral 'Choose Boring Technology' trend with 1,357 upvotes proves: stability beats novelty when building mission-critical systems.</t>
-  </si>
-  <si>
-    <t>Drop your favorite 'boring' tech tool in the comments and tell us why you stick with it! 👇</t>
-  </si>
-  <si>
-    <t>#BoringTechnology #SoftwareEngineering #DevLife #TechTrends #StabilityFirst #AIInDevelopment #CodeReview #EngineeringStrategy</t>
-  </si>
-  <si>
-    <t>Offering tech support for seniors? Here’s how you can help them stay connected with family through video calls and social media—just like my post that went viral helping 1,276 people solve their tech worries[2][3].</t>
-  </si>
-  <si>
-    <t>I help seniors with technology issues—because staying connected with family via Facebook and video calls is a powerful motivator for older adults to embrace new tech[2][3]. Join the conversation and share your story[1].</t>
-  </si>
-  <si>
-    <t>As a tech advocate for seniors, I’m bridging the digital divide by helping adults 50+ master tools that enhance daily life and family connection—88% of this group already use social media, with Facebook and YouTube leading[2][3].</t>
-  </si>
-  <si>
-    <t>I help seniors with technology issues—turning frustration into connection. Video calls &amp; Facebook are top motivators for older adults trying new tech. 1,276 upvotes prove this matters[1][2][3].</t>
-  </si>
-  <si>
-    <t>Seniors don’t need to be tech experts—they just need someone to help them start. From vocalizing labels to organizing thoughts, every small tech win builds confidence. Let’s make tech friendly for all ages[2][3].</t>
-  </si>
-  <si>
-    <t>What if the biggest barrier for seniors isn’t age—but lack of guided support? I help them overcome tech stress so they can connect, learn, and thrive[1][2].</t>
-  </si>
-  <si>
-    <t>DM me if you or a loved one needs personalized tech help—or tag a senior who deserves to feel confident with their devices[1][3].</t>
-  </si>
-  <si>
-    <t>#SeniorTechHelp #TechForSeniors #AgingParents #DigitalInclusion #HelpSeniors #TechSupport #SeniorCare #ConnectWithFamily #ElderTech #TechTipsForSeniors</t>
-  </si>
-  <si>
-    <t>Big moves: $Famous_company just switched to $Hyped_technology! 🚀 See why 1,200+ Reddit users are buzzing about this tech shift and what it means for your business. Swipe to learn the 5 phases of tech adoption →</t>
-  </si>
-  <si>
-    <t>We saw the trend: $Famous_company has officially switched to $Hyped_technology. With 1,224 upvotes and 200 comments on Reddit, this move is sparking major conversation. Is your company ready to follow? Learn how to navigate the hype cycle and avoid the 'Trough of Disillusionment' before it hits.</t>
-  </si>
-  <si>
-    <t>$Famous_company’s strategic switch to $Hyped_technology signals a pivotal moment in emerging tech adoption. As highlighted in recent Reddit discussions (1,224 upvotes), this move aligns with the 'Peak of Inflated Expectations' in the Gartner Hype Cycle. Organizations should evaluate internal readiness—infrastructure, budget, and skill levels—before committing to full-scale implementation. Consider phased pilots to assess tangible value before the hype subsides.</t>
-  </si>
-  <si>
-    <t>$Famous_company just switched to $Hyped_technology 🚀 Reddit is buzzing (1,224 upvotes!). Are you at the Peak of Inflated Expectations or ready for the Slope of Enlightenment? Don’t get stuck in the Trough of Disillusionment—plan your pilot first.</t>
-  </si>
-  <si>
-    <t>POV: Your company’s about to switch to $Hyped_technology like $Famous_company did 🤯 Reddit’s obsessed (1,200+ upvotes!). But is it real or just hype? Let’s break down the 5 stages of the Gartner Hype Cycle so you don’t end up in the disillusionment trough 👇</t>
-  </si>
-  <si>
-    <t>$Famous_company just switched to $Hyped_technology—and 1,200+ Reddit users are asking: Is this the real breakthrough or just another hype cycle trap?</t>
-  </si>
-  <si>
-    <t>Download our free guide on navigating the Gartner Hype Cycle and avoiding the 'Trough of Disillusionment'—start your pilot program today.</t>
-  </si>
-  <si>
-    <t>#HypeCycle #TechAdoption #EmergingTech #Gartner #DigitalTransformation #FamousCompany #HypedTechnology #TechTrends #Innovation #CIO</t>
-  </si>
-  <si>
-    <t>🚨 Big privacy alert: Apple’s proposed CSAM scanning tech is being called 'privacy-invasive' by experts. Thousands signed an open letter against it. Should we trust companies to scan our phones—even for 'good' reasons? 👇
-#PrivacyMatters #ApplePrivacy #DataSecurity #TechEthics #NoMoreScanning</t>
-  </si>
-  <si>
-    <t>An open letter against Apple’s privacy-invasive content scanning technology has gained over 1,100 upvotes and 670 comments on Reddit. Critics argue the system—which scans photos before iCloud upload to detect child sexual abuse material—bypasses end-to-end encryption and creates serious security risks. Top cryptographers say it’s unworkable and vulnerable to abuse. Is child safety worth compromising your private data?
-🔗 Join the discussion.
-#ApplePrivacy #CSAMScanning #DigitalRights #PrivacyFirst #TechNews</t>
-  </si>
-  <si>
-    <t>Apple’s proposed client-side CSAM scanning technology has sparked intense backlash from privacy advocates, cryptographers, and internet pioneers. The system, which scans iPhone photos before iCloud upload to detect known child sexual abuse material, raises concerns about bypassing end-to-end encryption and enabling future surveillance expansion. In August 2021, Apple announced the feature; in December 2022, it quietly abandoned the plan, shifting focus to Advanced Data Protection with end-to-end encryption[7].
-Key takeaways:
-• Over 1,100 Reddit users supported an open letter against the tech[5]
-• Scientists warn it creates serious privacy and security risks[1]
-• Apple claimed the feature was 'widely misunderstood'[3]
-• The plan was ultimately abandoned due to controversy[7]
-As organizations evaluate tech partnerships, this case underscores the need for transparent, privacy-preserving child safety measures.
-#TechPolicy #Privacy #Cybersecurity #Apple #ChildSafety #DigitalRights</t>
-  </si>
-  <si>
-    <t>🔥 Reddit explodes: 1,187 upvotes, 670 comments on 'An Open Letter Against Apple's Privacy-Invasive Content Scanning Technology'
-Critics say Apple’s CSAM scanner bypasses encryption &amp; creates security risks. Top cryptographers call it 'hazardous'[1][4]. Apple later abandoned the plan in 2022[7].
-Is safety worth invading privacy?
-#ApplePrivacy #CSAM #DataSecurity #TechEthics</t>
-  </si>
-  <si>
-    <t>🚨 STOP what you’re doing—Apple tried to scan YOUR phone photos. 
-→ Called it 'child safety'
-→ But experts said it’s privacy-invasive &amp; dangerous
-→ Over 1,000 people signed an open letter against it
-→ Apple quietly dropped the plan in 2022
-Should tech companies scan your data—even for good reasons? 🤔
-Comment your take! 👇
-#ApplePrivacy #TechNews #PrivacyMatters #CSAM #DigitalRights #fyp</t>
-  </si>
-  <si>
-    <t>Should Apple scan your phone photos to catch child abuse—or is that a privacy nightmare?</t>
-  </si>
-  <si>
-    <t>Share your opinion: Is child safety worth compromising your private data? Drop your take below 👇</t>
-  </si>
-  <si>
-    <t>#ApplePrivacy #CSAM #DataSecurity #TechEthics #PrivacyMatters #DigitalRights #NoMoreScanning #TechNews #Cybersecurity #ChildSafety</t>
-  </si>
-  <si>
-    <t>Big Tech is pouring nearly $1B into carbon removal startups like direct air capture and biochar. 🌍✨ From tree planting to novel tech, the future of climate action is scaling fast. Which method do you trust most? #CarbonRemoval #ClimateTech</t>
-  </si>
-  <si>
-    <t>Major tech companies including Stripe, Alphabet, Meta, and Shopify have committed nearly $1 billion to early-stage carbon removal startups. While conventional methods like tree planting account for 99% of current removal, less than 1% comes from novel tech like direct air capture. The market is expanding rapidly to fight climate change. 🌱💻 #CarbonRemoval #ClimateAction</t>
-  </si>
-  <si>
-    <t>The carbon removal market is scaling rapidly, with major tech firms committing nearly $1B to early-stage startups experimenting with direct air capture, biochar, and enhanced weathering. Yet, less than 1% of global CO₂ removal relies on these novel approaches compared to conventional methods like forest management. As attention and positive sentiment toward CDR grow exponentially on social media, the industry must balance innovation with proven biological sinks. #CarbonRemoval #ClimateTech #Sustainability</t>
-  </si>
-  <si>
-    <t>Big Tech is pouring $1B into carbon removal startups. 🚀 But less than 1% of global CO₂ removal uses novel tech like direct air capture. Most still relies on tree planting &amp; forest management. The race to scale CDR is heating up. #CarbonRemoval #ClimateTech</t>
-  </si>
-  <si>
-    <t>Why are Stripe, Meta &amp; Alphabet spending $1B on carbon removal? 🤔 Because we need more than just trees! From direct air capture to biochar, novel tech is finally getting funding. But right now, it's &lt;1% of all removal. 🌍⚡ #CarbonRemoval #ClimateChange #TechNews</t>
-  </si>
-  <si>
-    <t>Big Tech just committed $1B to carbon removal—but novel tech makes up less than 1% of what we remove today. 🌍</t>
-  </si>
-  <si>
-    <t>Which carbon removal method should get more funding? Vote in the comments and share your favorite tech! 👇</t>
-  </si>
-  <si>
-    <t>#CarbonRemoval #ClimateTech #CDR #DirectAirCapture #ClimateAction #Sustainability #GreenTech #NetZero</t>
-  </si>
-  <si>
-    <t>🚀 Low-code is eating software development! Developers on Reddit are watching Hasura, Strapi, Forest Admin, Integromat, Appgyver, and NodeRed. By 2026, 75% of new enterprise apps will be built with low-code/no-code [1][7]. AI integration is now the top trend shaping 2026 [1][4]. What’s on your tech watchlist? 🛠️💻</t>
-  </si>
-  <si>
-    <t>🔥 Big Reddit Trend Alert: 'Ask HN: What startup/technology is on your to-watch list?' got 1,006 upvotes and 669 comments! Top picks: Hasura, Strapi, Forest Admin, Integromat, Appgyver, and NodeRed. These are mostly low-code tools, but the community wants more upcoming tech making waves. Why low-code? Gartner predicts 75% of new applications will be low-code by 2026 [7]. AI + low-code = 363% ROI in 3 years [7]. Citizen developers are leading this shift [4][5]. What tech are you watching in 2026?</t>
-  </si>
-  <si>
-    <t>📈 Reddit Trend Breakdown: 'Ask HN: What startup/technology is on your to-watch list?' attracted 1,006 upvotes and 669 comments. Top low-code tools highlighted: Hasura, Strapi, Forest Admin, Integromat, Appgyver, and NodeRed. The low-code market surpassed $30B in 2026, driven by enterprise demand for faster delivery and developer shortages [6]. Gartner forecasts 75% of new enterprise applications will use low-code/no-code by 2026 [7]. Key 2026 trends: AI/GA integration [1][4], citizen developers [4], mobile-first platforms [4], DevOps collaboration [4], and legacy system modernization [4]. Organizations using AI-powered low-code platforms achieved 363% ROI [7]. This is no longer experimental—it’s the backbone of digital transformation [7].</t>
-  </si>
-  <si>
-    <t>🚨 Reddit Trend: 'What startup/tech is on your to-watch list?' → 1,006 upvotes, 669 comments. Top picks: Hasura, Strapi, Forest Admin, Integromat, Appgyver, NodeRed. All low-code! 🛠️ Gartner: 75% of new enterprise apps will be low-code by 2026 [7]. AI + low-code = 363% ROI [7]. Citizen devs leading the shift [4]. What’s on your list?</t>
-  </si>
-  <si>
-    <t>🔥 Reddit just dropped a HUGE tech trend! 1,006 upvotes, 669 comments asking: 'What startup/tech is on your to-watch list?' Top answers: Hasura, Strapi, Forest Admin, Integromat, Appgyver, NodeRed. All low-code! 🛠️ Why? 75% of new apps will be low-code by 2026 [7]. AI + low-code = 363% ROI [7]. Citizen developers are changing tech forever [4]. What tech are YOU watching? Drop it below! 👇</t>
-  </si>
-  <si>
-    <t>Low-code is eating software development—and Reddit developers are watching Hasura, Strapi, Forest Admin, Integromat, Appgyver, and NodeRed. By 2026, 75% of new enterprise apps will be built with low-code [7].</t>
-  </si>
-  <si>
-    <t>What startup or technology is on your 'to watch' list in 2026? Share your picks below! 👇</t>
-  </si>
-  <si>
-    <t>#LowCode #NoCode #TechTrends2026 #StartupWatchlist #Hasura #Strapi #ForestAdmin #Integromat #Appgyver #NodeRed #AIDev #CitizenDeveloper #DigitalTransformation #SoftwareDevelopment #TechCommunity</t>
-  </si>
-  <si>
-    <t>🚀 Daily tech news just got a upgrade! If you're glued to Hacker News, you need these 5 must-follow tech blogs: The Verge for gadget reviews &amp; AI insights, TechCrunch for startup moves, Wired for tech-science-culture intersections, CNET for product reviews, and Mashable for digital culture. Start your day smarter! 💻✨</t>
-  </si>
-  <si>
-    <t>🔥 Hacker News fans asked: 'What are good tech blogs to follow daily?' Here's the community's top picks: The Verge (gadget reviews, AI), TechCrunch (startup news), Wired (tech + science + culture), CNET (product reviews), and Mashable (digital lifestyle). 893 upvotes can't be wrong—add these to your feed now! 👇</t>
-  </si>
-  <si>
-    <t>📊 Key Insight: Following Hacker News alone isn't enough for daily tech depth. Per a trending Reddit thread (893 upvotes), top daily tech blogs include The Verge (AI/gadgets), TechCrunch (startups/investments), Wired (tech-science-culture), CNET (reviews), and Mashable (digital culture). IT leaders should also consider MartinFowler.com, Krebs on Security, and ZDNet for strategic depth. Stay ahead of the curve.</t>
-  </si>
-  <si>
-    <t>🚨 Hacker News fans: What else to follow daily? Top Reddit picks: The Verge (AI/gadgets), TechCrunch (startups), Wired (tech+science), CNET (reviews), Mashable (digital life). 893 upvotes agree—these are your daily must-reads. #TechBlogs #HackerNews</t>
-  </si>
-  <si>
-    <t>POV: You only read Hacker News but need MORE daily tech content 😱 Reddit's 893-upvote thread says: ↓
-1. The Verge (AI + gadgets)
-2. TechCrunch (startups)
-3. Wired (tech + science)
-4. CNET (reviews)
-5. Mashable (digital life)
-Save this list! 💾✨</t>
-  </si>
-  <si>
-    <t>If you check Hacker News daily but still feel behind on tech trends, you're missing these 5 elite blogs that 893 Reddit users swear by.</t>
-  </si>
-  <si>
-    <t>Save this post and start following these blogs today—your daily tech intel just got a massive upgrade! 👇</t>
-  </si>
-  <si>
-    <t>#TechBlogs #HackerNews #TechNews #StartupNews #AITrends #GadgetReviews #WiredMagazine #TechCrunch #TheVerge #CNET #Mashable #DailyTech #TechCommunity #DeveloperResources #ITLeaders</t>
+    <t>Images\The boring technology behind a one-person Internet company (2018).jpg</t>
+  </si>
+  <si>
+    <t>Images\How Technology Hijacks People’s Minds.jpg</t>
+  </si>
+  <si>
+    <t>Images\Extremely disillusioned with technology. Please help.jpg</t>
+  </si>
+  <si>
+    <t>Images\Choose Boring Technology.jpg</t>
+  </si>
+  <si>
+    <t>Images\I help seniors with technology issues.jpg</t>
+  </si>
+  <si>
+    <t>Images\We at $Famous_company switched to $Hyped_technology.jpg</t>
+  </si>
+  <si>
+    <t>Images\An Open Letter Against Apple's Privacy-Invasive Content Scanning Technology.jpg</t>
+  </si>
+  <si>
+    <t>Images\Carbon Removal Technologies.jpg</t>
+  </si>
+  <si>
+    <t>Solo founders don't need flashy tech stacks—they thrive on boring, stable, and proven tools that keep things simple and customer-focused. From Ruby on Rails to No-Code CRMs, the key is avoiding complexity and staying lean. Solo dev success = boring tech + automation + focus.</t>
+  </si>
+  <si>
+    <t>Why do the most profitable one-person internet companies run on 'boring' technology? Because stable, well-supported stacks like Ruby on Rails or Laravel reduce risk, speed up delivery, and let solo founders focus on what matters: their product and customers. Don't chase hype—embrace the boring.</t>
+  </si>
+  <si>
+    <t>For solopreneurs building profitable internet companies, 'boring technology' isn't a drawback—it's a strategic advantage. Proven monolithic frameworks (like Ruby on Rails or Laravel), PaaS/BaaS providers, and usage-based pricing tools minimize risk, avoid distributed system pitfalls, and accelerate iteration. The best tech stack is the one that keeps you focused on your customers.</t>
+  </si>
+  <si>
+    <t>Solo founders = boring tech winners. Stable stacks like Ruby on Rails + PaaS/BaaS + usage-based tools = less risk, faster delivery, more focus on customers. Stop chasing hype. Embrace the boring. 🚀 #Solopreneur #BoringTech</t>
+  </si>
+  <si>
+    <t>POV: You're a one-person internet company and everyone's asking 'what tech stack do you use?' You: 'Literally boring stuff.' 🔥 Ruby on Rails, Laravel, Notion CRM, MoR for billing. Why? Stable, proven, no manutenzione nightmares. Boring = fast, safe, profitable. #SolopreneurLife #BoringTech #StartupTips</t>
+  </si>
+  <si>
+    <t>The secret behind profitable one-person internet companies isn't cutting-edge tech—it's boring, stable, and proven technology.</t>
+  </si>
+  <si>
+    <t>Want to build a lean, scalable solo startup? Start with boring tech, automate the rest, and focus on your customers.</t>
+  </si>
+  <si>
+    <t>#Solopreneur #BoringTech #StartupTips #OnePersonCompany #RubyOnRails #Laravel #NoCode #TechStack #SoloDev #StartupStrategy</t>
+  </si>
+  <si>
+    <t>Social media platforms don't just distract us—they hijack our minds by exploiting dopamine-driven feedback loops. From Instagram to TikTok, algorithms are designed to trap attention, turning passive scrolling into unconscious conditioning. The tech industry knows this, and it's time we demand better design. #TechHijack #MindFreedom</t>
+  </si>
+  <si>
+    <t>A viral Reddit thread is exposing how modern technology hijacks our minds—turning apps into digital Skinner Boxes that exploit our psychology for profit. Former Google design ethicist Tristan Harris warns that platforms like Facebook, YouTube, and Instagram are reshaping how 2 billion people think daily. We're not just users; we're being manipulated. Let's fight for time well spent.</t>
+  </si>
+  <si>
+    <t>Technology isn't just shaping behavior—it's rewiring cognition. A trending discussion highlights how social media platforms use intermittent variable rewards, illusion of free choice, and fear-based triggers to hijack attention. Tristan Harris, former Google product manager, argues that tech giants now exert more influence over daily cognition than governments or religions. For leaders and professionals, this is a critical issue affecting productivity, mental health, and decision-making. We must prioritize ethical design and 'Time Well Spent' principles.</t>
+  </si>
+  <si>
+    <t>Tech is hijacking our minds. Reddit trend: 'How Technology Hijacks People’s Minds' exposes how apps use dopamine loops, fear triggers, and variable rewards to trap attention. From Instagram to TikTok, algorithms are conditioning us. Former Google ethicist Tristan Harris: 'Tech shapes thoughts of 2B people daily.' This is bigger than distraction. It's cognitive manipulation. #TechHijack #DigitalWellness</t>
+  </si>
+  <si>
+    <t>Your phone isn't just distracting you—it's hijacking your brain. 🧠📱 Algorithms use dopamine, fear, and reward loops to keep you scrolling. Reddit's trending post 'How Technology Hijacks People's Minds' reveals how TikTok, Instagram, and others act like digital Skinner Boxes. Tristan Harris says tech now influences 2B people's thoughts daily. Are you in control? Or is the app? #MindHijack #TechAwareness #StopScrolling</t>
+  </si>
+  <si>
+    <t>Your phone isn't just distracting you—it's actively hijacking your brain.</t>
+  </si>
+  <si>
+    <t>Share this post to spread awareness, then audit your app usage today. What's one platform you'll limit this week?</t>
+  </si>
+  <si>
+    <t>#TechHijack #DigitalWellness #MindFreedom #StopScrolling #TristanHarris #TimeWellSpent #CognitiveHacking #SocialMediaAwareness #Neuroplasticity #EthicalDesign</t>
+  </si>
+  <si>
+    <t>Feeling extremely disillusioned with technology lately? It's not just you. Many are hitting a wall with constant digital noise, AI fatigue, and the pressure to always be 'online.' Let's unpack why and how to find balance again. 🌱💻</t>
+  </si>
+  <si>
+    <t>Is technology making you feel more disconnected than ever? A recent Reddit post with 1500+ upvotes shows thousands are feeling extremely disillusioned with tech. From AI overwhelm to social media burnout, here's how we can reclaim our humanity in a digital world.</t>
+  </si>
+  <si>
+    <t>The growing trend of tech disillusionment is real. A viral Reddit thread titled 'Extremely disillusioned with technology' has sparked 700+ comments, reflecting widespread fatigue with automation, data privacy concerns, and the erosion of authentic human connection. Professionals are now seeking sustainable tech strategies that prioritize well-being over constant innovation.</t>
+  </si>
+  <si>
+    <t>Extremely disillusioned with technology? 1,500+ Reddit users feel the same. Tech fatigue is real — from AI pressure to digital burnout. Let's talk about finding balance. 🧠⚡️</t>
+  </si>
+  <si>
+    <t>POV: You're so done with technology. 😩 1,500+ people on Reddit just said the same. Tech burnout is NOT a you problem. Let's break down why we're all feeling this and how to reset. 📱❌ #techfatigue</t>
+  </si>
+  <si>
+    <t>Why are so many people suddenly extremely disillusioned with technology?</t>
+  </si>
+  <si>
+    <t>Share your tech burnout story in the comments and let's build a community for mindful digital living.</t>
+  </si>
+  <si>
+    <t>#TechDisillusionment #DigitalBurnout #TechFatigue #MindfulTech #AIOverload #SocialMediaBurnout #TechReset #DigitalWellness</t>
+  </si>
+  <si>
+    <t>✨ Choose boring tech, not shiny new tools. 🛠️ The smartest devs pick what’s known, reliable, and lets them focus on what matters. Less innovation tokens = more success. 💡 #BoringTech #DevLife #StableStack</t>
+  </si>
+  <si>
+    <t>Tired of chasing the latest tech trend? Here’s a truth: Choose boring technology. It’s well-understood, has known failure modes, and helps you focus on solving real problems—not wrestling with new tools. 🧱💻 Learn more at boringtechnology.club</t>
+  </si>
+  <si>
+    <t>In an era of AI-generated code and rapid innovation, ‘Choose Boring Technology’ remains a powerful principle. Prefer tools that are well-understood, with known failure modes, and that let you focus on what truly matters. Stability &gt; Shiny. 🛠️📈 #SoftwareEngineering #BoringTech #TechStrategy</t>
+  </si>
+  <si>
+    <t>🚫 Not another new framework. ✅ Choose boring tech. It’s reliable, understood, and lets you focus on solving real problems. Less hype, more stability. #BoringTech #DevTips #SoftwareEngineering</t>
+  </si>
+  <si>
+    <t>Why choose BORING tech over shiny new stuff? 🤔 Because it’s stable, predictable, and lets you actually solve problems instead of debugging new tools. 🛠️💻 Swing through boringtechnology.club for the full story! #BoringTech #DevLife #TechTok</t>
+  </si>
+  <si>
+    <t>Stop chasing shiny new tech. The smartest engineers choose boring, reliable tools that get the job done.</t>
+  </si>
+  <si>
+    <t>Visit boringtechnology.club to learn why boring tech wins—and how to apply it to your next project.</t>
+  </si>
+  <si>
+    <t>#BoringTech #SoftwareEngineering #DevLife #TechStrategy #StableStack #CodeQuality #NoHype</t>
+  </si>
+  <si>
+    <t>👵👴 Helping seniors feel confident with tech! From setting up video calls to navigating social media, I break down technology into simple, stress-free steps. No judgment, just patience and practical tips. 💙✨ #SeniorTech #TechForSeniors</t>
+  </si>
+  <si>
+    <t>I help seniors overcome technology challenges with one-on-one support and personalized training. Whether it's staying connected through video calls, using Facebook safely, or managing online bills, I make tech easy and empowering for older adults. Let’s bridge the gap together! 🌐👴👵</t>
+  </si>
+  <si>
+    <t>Offering specialized technology support for seniors to enhance digital inclusion and independence. My services include personalized device training, safe social media usage, remote connectivity setup, and confidence-building workshops that empower older adults to thrive in a digital world.</t>
+  </si>
+  <si>
+    <t>👴👵 Tech too hard? I help seniors master it! From video calls to Facebook safety, I make technology simple, safe, and fun. No jargon, just real help. Let’s get you connected! 💻✨ #SeniorTech #TechSupport #AgingAndTechnology</t>
+  </si>
+  <si>
+    <t>👵👴 Wait, seniors can use tech like this?! 😲 I help older adults finally feel confident with their phones, tablets, and computers. Think: video calls with grandkids, safe Facebook use, and no more ‘I’m stuck’ moments! Follow for easy, step-by-step tech tips made for seniors! 📱💙 #SeniorTech #TechForSeniors #ElderCare</t>
+  </si>
+  <si>
+    <t>Tech feels overwhelming for many seniors—but it shouldn't. I help older adults master phones, tablets, and apps with calm, clear, step-by-step guidance.</t>
+  </si>
+  <si>
+    <t>Book a free 15-minute tech consult today and get your first challenge solved—no pressure, just support!</t>
+  </si>
+  <si>
+    <t>#SeniorTech #TechForSeniors #AgingAndTechnology #DigitalInclusion #ElderCare #TechSupport #SeniorLiving #AgeFriendly #SmartSeniors #HelpingSeniors</t>
+  </si>
+  <si>
+    <t>We at $Famous_company just switched to $Hyped_technology — and the results are already in. Swipe to see what’s possible when bold brands embrace cutting-edge tech. ✨</t>
+  </si>
+  <si>
+    <t>Big move alert: $Famous_company has officially switched to $Hyped_technology! Our team is excited to share how this change is transforming our workflow and customer experience. What do you think about this tech shift?</t>
+  </si>
+  <si>
+    <t>$Famous_company has made a strategic decision to switch to $Hyped_technology — a move aligned with our commitment to innovation and efficiency. As industry leaders continue to evaluate emerging tools, we’re proud to lead the way in adopting solutions that drive real business value.</t>
+  </si>
+  <si>
+    <t>🚨 BREAKING: $Famous_company just switched to $Hyped_technology. The team’s already seeing the impact. Are you ready to join the shift? 🔥</t>
+  </si>
+  <si>
+    <t>POV: You’re at $Famous_company and we just switched to $Hyped_technology. 🤯 Here’s what changed in 24 hours. #TechUpdate #WorkplaceVibes</t>
+  </si>
+  <si>
+    <t>We at $Famous_company switched to $Hyped_technology — and everything changed in 24 hours.</t>
+  </si>
+  <si>
+    <t>Discover how $Hyped_technology is reshaping industries — and why $Famous_company made the switch. Learn more now.</t>
+  </si>
+  <si>
+    <t>#HypedTechnology #FamousCompany #TechTrend #Innovation #DigitalTransformation #StartupLife #TechUpdate</t>
+  </si>
+  <si>
+    <t>🚨 Privacy alert: Apple’s proposed CSAM scanning tech was condemned by top cryptographers as a threat to security and privacy. The open letter against it gathered thousands of signatures before Apple quietly abandoned the plan in 2022 [1][2][5]. Now that Advanced Data Protection encrypts your iCloud data, you hold the keys—not Apple [5]. Stay informed, stay private. #PrivacyFirst</t>
+  </si>
+  <si>
+    <t>Apple once proposed scanning your photos for child abuse material before they hit iCloud. But leading experts said it was flawed, vulnerable to abuse, and a privacy risk [1][4]. An open letter against the tech gained massive support, and Apple dropped the plan in late 2022 [2][5]. Instead, they expanded end-to-end encryption so only YOU control your data [5]. Your privacy matters—learn more and protect it.</t>
+  </si>
+  <si>
+    <t>In 2021, Apple proposed client-side scanning of iCloud photos to detect known CSAM, using NeuralHash and Private Set Intersection [5]. However, cryptographic experts and internet pioneers condemned it as unworkable and a security risk [1][4]. An open letter against the technology attracted thousands of signatures, prompting Apple to abandon the initiative in December 2022 [2][5]. The company subsequently prioritized Advanced Data Protection, strengthening end-to-end encryption so users retain exclusive control of their keys [5]. This case underscores the critical balance between child safety and user privacy in tech policy.</t>
+  </si>
+  <si>
+    <t>🚫 Apple’s CSAM photo-scanning plan was scrapped after cryptographers called it a privacy/security threat. Open letter gained thousands of signatures → Apple abandoned it in Dec 2022 [1][2][5]. Now, Advanced Data Protection = YOU hold the keys to iCloud [5]. #Privacy #Apple #CSAM</t>
+  </si>
+  <si>
+    <t>Apple tried to scan your photos for child abuse stuff before they went to iCloud. But experts said: NOPE—it’s a privacy nightmare and security risk [1][4]. An open letter got thousands of signatures... and Apple dropped the plan in 2022 [2][5]. Now, your iCloud is encrypted with keys YOU control [5]. Privacy wins again. 🔐 #TechNews #Privacy #AppleExposed</t>
+  </si>
+  <si>
+    <t>Apple tried to scan your photos—but top experts said it was a privacy disaster. Here’s why they stopped.</t>
+  </si>
+  <si>
+    <t>Learn how to activate Advanced Data Protection and keep your iCloud data fully encrypted—with keys only you hold.</t>
+  </si>
+  <si>
+    <t>#PrivacyFirst #ApplePrivacy #CSAM #DataProtection #TechEthics #EndToEndEncryption #OpenLetter #DigitalRights</t>
+  </si>
+  <si>
+    <t>Big Tech is pouring nearly $1B into carbon removal startups like those using direct air capture [4]. While interest in carbon removal is growing exponentially and sentiment is positive, scaling technologies like DAC to gigaton levels remains highly uncertain [2][3][5].</t>
+  </si>
+  <si>
+    <t>Carbon removal technologies are gaining massive attention, with Stripe, Alphabet, Meta, and Shopify committing nearly $1 billion to early-stage startups [4]. However, experts warn that current strategies rely on overly optimistic assumptions about direct air capture (DAC) deployment [5].</t>
+  </si>
+  <si>
+    <t>The carbon removal market is expanding rapidly as major tech firms invest nearly $1B in startups experimenting with carbon capture and sequestration [4]. Despite rising corporate investment and US federal spending exceeding $80M, the industry faces challenges: many firms have ceased operations, and scaling DAC to gigaton levels is 'highly uncertain' [5][6]. Government support is likely critical for the industry to flourish [6].</t>
+  </si>
+  <si>
+    <t>Big Tech is pouring $1B into carbon removal tech like direct air capture (DAC) [4]. But MIT researchers say scaling DAC to gigaton levels is 'highly uncertain' and current strategies rely on unrealistic assumptions [5]. CDR attention grew exponentially on social media, with sentiment turning positive except for BECCS [2][3].</t>
+  </si>
+  <si>
+    <t>Why are Stripe, Alphabet, and Meta dumping $1B into carbon removal startups? [4] They're betting on tech like direct air capture to suck CO2 from the air [5]. But scientists say scaling this to remove billions of tonnes is 'highly uncertain' and might not work as predicted [5].</t>
+  </si>
+  <si>
+    <t>Big Tech just dropped nearly $1 billion into carbon removal tech—but can it actually scale?</t>
+  </si>
+  <si>
+    <t>Follow for more deep dives on the future of climate tech and carbon removal realities.</t>
+  </si>
+  <si>
+    <t>#CarbonRemoval #CleanTech #ClimateAction #DirectAirCapture #BigTech #Sustainability #CDR</t>
+  </si>
+  <si>
+    <t>🚀 Low-code is eating software dev: 70% of new enterprise apps now use low/no-code tools [2]. From Hasura to SAP Build (formerly AppGyver), these tools are reshaping how we build [1][3]. What’s on your ‘to watch’ list? 👇</t>
+  </si>
+  <si>
+    <t>Trending on Reddit: Devs are buzzing about low-code startups like Hasura, Strapi, Forest Admin, Integromat, and Appgyver. The low-code market hit $30B in 2026 and 70%+ of new enterprise apps now use these tools [1][2]. Citizen developers are rising, and AI-native app generation is the next wave [2][7]. What tech are you watching?</t>
+  </si>
+  <si>
+    <t>🔍 Ask HN: What startup/tech is on your ‘to watch’ list? The Reddit thread highlights low-code leaders like Hasura, Strapi, Forest Admin, Integromat, and Appgyver (now SAP Build Apps) [1][3]. In 2026, low-code crossed $30B, with over 70% of new enterprise apps built using low/no-code [2]. AI-native generation and citizen developers are defining the next era [2][7]. Are you tracking low-code?</t>
+  </si>
+  <si>
+    <t>🚨 Reddit trend: Devs rank Hasura, Strapi, Forest Admin, Integromat, Appgyver as top ‘to watch’ low-code startups [1]. Low-code market = $30B in 2026; 70%+ of new enterprise apps use it [2]. AI-native app gen + citizen devs = next wave [2][7]. What’s on your radar? #LowCode #StartupWatch</t>
+  </si>
+  <si>
+    <t>🔥 Low-code is EVERYWHERE in 2026. 70% of new apps use it, market hit $30B [2]. Reddit devs hype Hasura, Strapi, Forest Admin, Integromat, Appgyver [1]. AI + citizen devs = next wave [2][7]. What tech are you watching? 👀</t>
+  </si>
+  <si>
+    <t>Low-code isn’t niche—it’s now the dominant paradigm for enterprise apps, with 70%+ adoption in 2026 [2].</t>
+  </si>
+  <si>
+    <t>Drop your ‘to watch’ startup or tech below 👇</t>
+  </si>
+  <si>
+    <t>#LowCode #NoCode #StartupWatch #TechTrends2026 #AI #AppGyver #Hasura #Strapi #ForestAdmin #Integromat #DevCommunity #CitizenDevelopers #SAPBuild #ApplicationDevelopment</t>
+  </si>
+  <si>
+    <t>🚀 Daily tech news just got easier! If you're checking Hacker News, you NEED these blogs: TechCrunch for startups, The Verge for all-round coverage, and Wired for the big picture. Which one's your go-to? 👇
+#TechBlogs #TechNews #StartupLife #TechCrunch #TheVerge #Wired #HackerNews</t>
+  </si>
+  <si>
+    <t>🔥 Reddit Trend Alert: 893 upvotes on 'Best Tech Blogs to Follow'!
+Beyond Hacker News, top picks include:
+✅ TechCrunch – Startups &amp; funding
+✅ The Verge – Best all-round tech news
+✅ Wired – Tech + science depth
+✅ CNET &amp; TechRadar – Reviews &amp; buying advice
+✅ Ars Technica – Deep analysis
+Follow these for daily high-quality tech content! 💻
+#TechBlogs #TechnologyNews #HackerNews #TechCrunch #TheVerge #Wired</t>
+  </si>
+  <si>
+    <t>📈 High-Value Reddit Trend: 'Ask HN: What are good technology blogs to follow?'
+With 893 upvotes and 187 comments, tech professionals are seeking alternatives to Hacker News. Top recommendations:
+• TechCrunch: Leading source for startup news, funding, and product launches [1][9]
+• The Verge: Best all-round coverage for daily tech news [1][3]
+• Wired: Comprehensive tech &amp; science insights [1][3]
+• Ars Technica: Deep technical analysis [3]
+• CNET/TechRadar: Reviews and buying advice [3]
+For IT leaders, also consider ZDNet, ComputerWeekly, and Harvard Business Review [4].
+#TechBlogs #TechnologyLeadership #StartupNews #TechCrunch #TheVerge #Wired #HackerNews</t>
+  </si>
+  <si>
+    <t>🚨 Reddit Trend: 'Best Tech Blogs to Follow' (893 upvotes)
+Beyond Hacker News:
+→ TechCrunch: Startups &amp; funding [1][9]
+→ The Verge: All-round daily news [1][3]
+→ Wired: Tech + science [1][3]
+→ Ars Technica: Deep analysis [3]
+→ CNET: Reviews [3]
+Daily signal &gt; noise. Which do you follow? #TechBlogs #TechNews #HackerNews #TechCrunch</t>
+  </si>
+  <si>
+    <t>POV: You check Hacker News daily but need MORE tech content 🤯
+Reddit's trending post (893 upvotes) says:
+✅ TechCrunch = Startups &amp; funding
+✅ The Verge = Best daily news
+✅ Wired = Big picture + science
+✅ Ars Technica = Deep analysis
+✅ CNET = Reviews
+Tag your tech-savvy friend! 👯‍♀️💻
+#TechBlogs #TechNews #HackerNews #TechCrunch #TheVerge #Wired #TechTok</t>
+  </si>
+  <si>
+    <t>Hacker News isn't enough? 893 Reddit users agree — here are the top tech blogs to follow daily.</t>
+  </si>
+  <si>
+    <t>Follow these blogs now and stay ahead in tech — which one will you add first?</t>
+  </si>
+  <si>
+    <t>#TechBlogs #TechnologyNews #TechCrunch #TheVerge #Wired #HackerNews #StartupNews #TechReview #DigitalTrends #ArsTechnica</t>
   </si>
   <si>
     <t>Success</t>
-  </si>
-  <si>
-    <t>Images\The boring technology behind a one-person Internet company (2018).jpg</t>
-  </si>
-  <si>
-    <t>Images\How Technology Hijacks People’s Minds.jpg</t>
-  </si>
-  <si>
-    <t>Images\Extremely disillusioned with technology. Please help.jpg</t>
-  </si>
-  <si>
-    <t>Images\Choose Boring Technology.jpg</t>
-  </si>
-  <si>
-    <t>Images\I help seniors with technology issues.jpg</t>
-  </si>
-  <si>
-    <t>Images\We at $Famous_company switched to $Hyped_technology.jpg</t>
-  </si>
-  <si>
-    <t>Images\An Open Letter Against Apple's Privacy-Invasive Content Scanning Technology.jpg</t>
-  </si>
-  <si>
-    <t>Images\Carbon Removal Technologies.jpg</t>
   </si>
 </sst>
 </file>
@@ -454,10 +440,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -818,39 +800,39 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="144" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K2" t="s">
         <v>21</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>101</v>
-      </c>
-      <c r="K2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -858,34 +840,34 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K3" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -893,69 +875,69 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J4" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K4" t="s">
-        <v>104</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="216" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="J5" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K5" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -963,34 +945,34 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K6" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -998,34 +980,34 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J7" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K7" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
@@ -1033,34 +1015,34 @@
         <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I8" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J8" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K8" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1068,34 +1050,34 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F9" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J9" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="K9" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -1103,57 +1085,57 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="I10" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" t="s">
-        <v>95</v>
+      <c r="B11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G11" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H11" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I11" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
